--- a/web/Pipistrelli 2023.xlsx
+++ b/web/Pipistrelli 2023.xlsx
@@ -5030,11 +5030,6 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
       <c r="H87" t="n">
         <v>45.4083415</v>
       </c>
@@ -5084,11 +5079,6 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
       <c r="H88" t="n">
         <v>45.4083415</v>
       </c>
@@ -5239,11 +5229,6 @@
       <c r="F91" t="inlineStr">
         <is>
           <t>Barbarno Mossano</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>VI</t>
         </is>
       </c>
       <c r="H91" t="n">
